--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487428_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487428_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.165</v>
+        <v>6.3014</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2524</v>
+        <v>5.5759</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9126</v>
+        <v>0.7255</v>
       </c>
       <c r="G2" t="n">
         <v>5.5246</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3858</v>
+        <v>0.5221</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4882</v>
+        <v>-0.1647</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8739</v>
+        <v>0.6868</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3329</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.115</v>
+        <v>5.9991</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6619</v>
+        <v>3.8401</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4531</v>
+        <v>2.159</v>
       </c>
       <c r="G3" t="n">
         <v>1.4271</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3596</v>
+        <v>1.2438</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5087</v>
+        <v>0.6869</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8509</v>
+        <v>0.5568</v>
       </c>
       <c r="V3" t="n">
         <v>0.3905</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2875</v>
+        <v>4.9433</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6922</v>
+        <v>2.1609</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5953</v>
+        <v>2.7824</v>
       </c>
       <c r="G4" t="n">
         <v>1.8128</v>
@@ -766,13 +766,13 @@
         <v>3.5253</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3087</v>
+        <v>0.3471</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2923</v>
+        <v>0.1764</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0164</v>
+        <v>0.1707</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6055</v>
+        <v>3.8931</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6602</v>
+        <v>3.1884</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9453</v>
+        <v>0.7047</v>
       </c>
       <c r="G5" t="n">
         <v>3.1895</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0243</v>
+        <v>0.3119</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9504</v>
+        <v>-0.4223</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9747</v>
+        <v>0.7341</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2822</v>
+        <v>2.4858</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4563</v>
+        <v>1.4727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8259</v>
+        <v>1.013</v>
       </c>
       <c r="G6" t="n">
         <v>0.6806</v>
@@ -922,13 +922,13 @@
         <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2306</v>
+        <v>0.4342</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1059</v>
+        <v>0.1223</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1247</v>
+        <v>0.3119</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7801</v>
+        <v>2.0755</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0171</v>
+        <v>1.1788</v>
       </c>
       <c r="F7" t="n">
-        <v>0.763</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1.7922</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2079</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.297</v>
+        <v>-0.1353</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0891</v>
+        <v>0.2228</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7137</v>
+        <v>0.6929</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0014</v>
+        <v>0.0608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7123</v>
+        <v>0.6321</v>
       </c>
       <c r="G8" t="n">
         <v>0.3337</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1841</v>
+        <v>0.1634</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2435</v>
+        <v>0.1634</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4329</v>
+        <v>0.3847</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5931</v>
+        <v>-1.9626</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1601</v>
+        <v>2.3473</v>
       </c>
       <c r="G9" t="n">
         <v>0.5221</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7004</v>
+        <v>0.1172</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0692</v>
+        <v>-0.4388</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3688</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5322</v>
+        <v>-0.3064</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2135</v>
+        <v>-2.0947</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6814</v>
+        <v>1.7883</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0858</v>
@@ -1234,13 +1234,13 @@
         <v>3.1336</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8659</v>
+        <v>1.0916</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4493</v>
+        <v>0.5681</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4165</v>
+        <v>0.5234</v>
       </c>
       <c r="V10" t="n">
         <v>1.492</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7078</v>
+        <v>-0.5875</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0754</v>
+        <v>-0.2867</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3675</v>
+        <v>-0.3008</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0878</v>
+        <v>-0.1859</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3148</v>
+        <v>-1.1099</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7731</v>
+        <v>0.924</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9566</v>
+        <v>0.9443</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3148</v>
+        <v>-0.7724</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6418</v>
+        <v>1.7167</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1313</v>
+        <v>-1.1302</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.3375</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1313</v>
+        <v>-0.7927</v>
       </c>
       <c r="P11" t="n">
         <v>0.3917</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3917</v>
+        <v>2.3502</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0117</v>
+        <v>0.6987</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1188</v>
+        <v>0.7275</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1071</v>
+        <v>-0.0288</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2271</v>
+        <v>-0.7286</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7125</v>
+        <v>-1.016</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.2874</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1859</v>
+        <v>-1.0878</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1099</v>
+        <v>-0.3148</v>
       </c>
       <c r="I12" t="n">
-        <v>0.924</v>
+        <v>-0.7731</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9443</v>
+        <v>-0.9566</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7724</v>
+        <v>-0.3148</v>
       </c>
       <c r="L12" t="n">
-        <v>1.7167</v>
+        <v>-0.6418</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1302</v>
+        <v>-0.1313</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3375</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7927</v>
+        <v>-0.1313</v>
       </c>
       <c r="P12" t="n">
         <v>0.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3502</v>
+        <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.059</v>
+        <v>-0.0325</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3017</v>
+        <v>-0.0594</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2427</v>
+        <v>0.0269</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8955</v>
+        <v>-4.8117</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4668</v>
+        <v>-0.3158</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.3623</v>
+        <v>-4.4959</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1267</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1921</v>
+        <v>1.2758</v>
       </c>
       <c r="T13" t="n">
-        <v>2.936</v>
+        <v>1.1533</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2561</v>
+        <v>0.1225</v>
       </c>
       <c r="V13" t="n">
         <v>-3.1567</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.1535</v>
+        <v>20.3416</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6138</v>
+        <v>11.8018</v>
       </c>
       <c r="F14" t="n">
-        <v>8.5396</v>
+        <v>8.5397</v>
       </c>
       <c r="G14" t="n">
         <v>7.7964</v>
@@ -1546,13 +1546,13 @@
         <v>19.5847</v>
       </c>
       <c r="S14" t="n">
-        <v>5.072699999999999</v>
+        <v>6.2608</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0263</v>
+        <v>2.214</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0462</v>
+        <v>4.046399999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5496</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2082</v>
+        <v>4.6616</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4241</v>
+        <v>6.2194</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2159</v>
+        <v>-1.5578</v>
       </c>
       <c r="G15" t="n">
         <v>0.6577</v>
@@ -1624,13 +1624,13 @@
         <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6417</v>
+        <v>0.0951</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2988</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9405</v>
+        <v>0.5986</v>
       </c>
       <c r="V15" t="n">
         <v>1.5586</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MANEIRO SANCHEZ</t>
+          <t>P. FERNANDEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.523</v>
+        <v>0.3051</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1188</v>
+        <v>1.258</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4042</v>
+        <v>-0.9529</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4042</v>
+        <v>0.1602</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1.1282</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4042</v>
+        <v>1.2885</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.9633</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.3623</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.601</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4042</v>
+        <v>-2.8031</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.4905</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4042</v>
+        <v>-1.3126</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1188</v>
+        <v>-0.9792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1188</v>
+        <v>-0.9634</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.0159</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7325</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.4841</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>J. MANEIRO SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,22 +1735,22 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0469</v>
+        <v>-0.523</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0386</v>
+        <v>-0.1188</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0083</v>
+        <v>-0.4042</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2052</v>
+        <v>-0.4042</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2052</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.4042</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1762,31 +1762,31 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2052</v>
+        <v>-0.4042</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2052</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.4042</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2729</v>
+        <v>-0.1188</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0594</v>
+        <v>-0.1188</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2135</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.202</v>
+        <v>-1.0469</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6792</v>
+        <v>-1.0386</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4772</v>
+        <v>-0.0083</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3922</v>
+        <v>0.2052</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5887</v>
+        <v>0.2052</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8035</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0308</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3793</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6515</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3614</v>
+        <v>0.2052</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2094</v>
+        <v>0.2052</v>
       </c>
       <c r="O18" t="n">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6932</v>
+        <v>-0.2729</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7722</v>
+        <v>-0.0594</v>
       </c>
       <c r="U18" t="n">
-        <v>0.079</v>
+        <v>-0.2135</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ GONZALEZ</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2141</v>
+        <v>-1.1289</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4394</v>
+        <v>-0.103</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6535</v>
+        <v>-1.0259</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1602</v>
+        <v>-2.0212</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1282</v>
+        <v>-0.5158</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2885</v>
+        <v>-1.5054</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9633</v>
+        <v>-0.4858</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3623</v>
+        <v>0.6362</v>
       </c>
       <c r="L19" t="n">
-        <v>2.601</v>
+        <v>-1.122</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8031</v>
+        <v>-1.5354</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4905</v>
+        <v>-1.152</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3126</v>
+        <v>-0.3834</v>
       </c>
       <c r="P19" t="n">
         <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3502</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4985</v>
+        <v>-0.4407</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.7821</v>
+        <v>-0.4629</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7165</v>
+        <v>0.0222</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7325</v>
+        <v>0.9412</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2166</v>
+        <v>1.8249</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4841</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6082</v>
+        <v>-1.3061</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2053</v>
+        <v>-2.6792</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4029</v>
+        <v>1.3731</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0212</v>
+        <v>1.3922</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5158</v>
+        <v>0.5887</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5054</v>
+        <v>0.8035</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4858</v>
+        <v>1.0308</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6362</v>
+        <v>0.3793</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.122</v>
+        <v>0.6515</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5354</v>
+        <v>0.3614</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.152</v>
+        <v>0.2094</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3834</v>
+        <v>0.152</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3917</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.92</v>
+        <v>-0.7974</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5652</v>
+        <v>-0.7722</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3548</v>
+        <v>-0.0251</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9412</v>
+        <v>0.0576</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8837</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5966</v>
+        <v>-2.4187</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3082</v>
+        <v>-2.1036</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2884</v>
+        <v>-0.3151</v>
       </c>
       <c r="G21" t="n">
         <v>-1.012</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4095</v>
+        <v>-0.2316</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4158</v>
+        <v>-0.2111</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0063</v>
+        <v>-0.0204</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7366</v>
+        <v>-4.577</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3224</v>
+        <v>-3.43</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4142</v>
+        <v>-1.147</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7984</v>
+        <v>-1.3504</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.227</v>
+        <v>0.6908</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5714</v>
+        <v>-2.0411</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5567</v>
+        <v>0.0423</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5375</v>
+        <v>0.7554</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0193</v>
+        <v>-0.713</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3551</v>
+        <v>-1.3927</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7645</v>
+        <v>-0.0646</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5906</v>
+        <v>-1.3281</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7626</v>
+        <v>-2.546</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1543</v>
+        <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1483</v>
+        <v>-0.7472</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.18</v>
+        <v>-0.5346</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3283</v>
+        <v>-0.2126</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3239</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2178</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5417</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8739</v>
+        <v>-4.9652</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.43</v>
+        <v>-3.5271</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4439</v>
+        <v>-1.4381</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3504</v>
+        <v>-2.7984</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6908</v>
+        <v>-1.227</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0411</v>
+        <v>-1.5714</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0423</v>
+        <v>0.5567</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7554</v>
+        <v>0.5375</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.713</v>
+        <v>0.0193</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3927</v>
+        <v>-3.3551</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0646</v>
+        <v>-1.7645</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3281</v>
+        <v>-1.5906</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.546</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0441</v>
+        <v>-0.0803</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5346</v>
+        <v>-0.3846</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5094</v>
+        <v>0.3044</v>
       </c>
       <c r="V23" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.3239</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2178</v>
       </c>
       <c r="X23" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.5417</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5603</v>
+        <v>-6.7899</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3004</v>
+        <v>-3.0168</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2599</v>
+        <v>-3.7731</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6256</v>
@@ -2326,13 +2326,13 @@
         <v>1.3709</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.1353</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6805</v>
+        <v>-0.0359</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5861</v>
+        <v>-0.0994</v>
       </c>
       <c r="V24" t="n">
         <v>-1.483</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.1534</v>
+        <v>-17.789</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.539399999999999</v>
+        <v>-8.5397</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.614</v>
+        <v>-9.2493</v>
       </c>
       <c r="G25" t="n">
         <v>-7.7965</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.4577</v>
+        <v>-6.457700000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-1.3385</v>
       </c>
       <c r="J25" t="n">
-        <v>8.573</v>
+        <v>8.572999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6926</v>
+        <v>2.692600000000001</v>
       </c>
       <c r="L25" t="n">
         <v>5.8807</v>
@@ -2389,13 +2389,13 @@
         <v>-16.3696</v>
       </c>
       <c r="N25" t="n">
-        <v>-9.150400000000001</v>
+        <v>-9.150399999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-7.219200000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.8338</v>
+        <v>-7.833799999999998</v>
       </c>
       <c r="Q25" t="n">
         <v>-19.5848</v>
@@ -2404,13 +2404,13 @@
         <v>11.7508</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.0727</v>
+        <v>-3.7083</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.0464</v>
+        <v>-4.046399999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0262</v>
+        <v>0.3383</v>
       </c>
       <c r="V25" t="n">
         <v>1.5496</v>
@@ -2419,7 +2419,7 @@
         <v>6.5186</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.968999999999999</v>
+        <v>-4.969</v>
       </c>
     </row>
   </sheetData>
